--- a/verification/cases/roundtrip/font_theme_colours/init.xlsx
+++ b/verification/cases/roundtrip/font_theme_colours/init.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{53815DA9-1EE1-4D82-B0AD-168C4E5685DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,8 +28,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,17 +81,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -128,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -162,6 +171,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -196,9 +206,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -371,15 +382,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -394,9 +405,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
@@ -404,9 +415,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
